--- a/mapping/Mitochondrion.xlsx
+++ b/mapping/Mitochondrion.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B43"/>
+  <dimension ref="A1:B54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -932,6 +932,138 @@
         </is>
       </c>
     </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Actinidia</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>猕猴桃属</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Cucurbita</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>南瓜属</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Diospyros</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>柿属</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Phoenix</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>刺葵属（海枣属）</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Salix</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>柳属</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Triosteum</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>莲子薰属</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Bruguiera</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>木榄属</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Jatropha</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>麻风树属</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Ziziphus</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>枣属</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gorilla</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>大猩猩属</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Trichosporon</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>毛孢子菌属</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
